--- a/publications.xlsx
+++ b/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SeDire-lab.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA2CDAA-6CD1-45BE-ABBA-8430E715F960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C65479-3F22-45F4-82A2-31B9AF683862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{349F55B1-14CC-4F4D-9FA7-70B935E84A00}"/>
+    <workbookView xWindow="1800" yWindow="1536" windowWidth="17280" windowHeight="9108" xr2:uid="{349F55B1-14CC-4F4D-9FA7-70B935E84A00}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">publications!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
